--- a/data/env_test/case_excle/CompanyPurchars/case_data_zz.xlsx
+++ b/data/env_test/case_excle/CompanyPurchars/case_data_zz.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10119"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10209"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Lucas/PycharmProjects/InterfaceAutomaticTesttPlatform/data/env_test/case_excle/zz/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Lucas/PycharmProjects/InterfaceAutomaticTesttPlatform/data/env_test/case_excle/CompanyPurchars/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13F768D4-CC44-A04F-98AD-4977478A433D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54F6464F-0AE7-6647-A7CD-EBF97EEEFEC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="36000" yWindow="500" windowWidth="51200" windowHeight="27040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -572,7 +572,7 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>{"scaleProcess":2,"ifOfferRank":"false","ifWeight":"false","ifCreditScore":"false","scorePrincipleType":0,"reviewer":"1","methodName":"0","ifCreditWeight":"false","ifSupportPreviewSumScore":"true","scorePrincipleParam":"{\"ruleContent\":\"汇总全部评分后，计算评分均值\"}","creditScoreParam":"{}","tfId":"${tfId}","steps":[{"ifPqr":"true","ifSummarize":"false","ifReject":"false","ifBlindBid":"false","rejectType":1,"ifOpenComputeChange":"false","isExpand":"false","stepName":"资格评审","sort":1,"stepType":0,"items":[{"itemName":"测试","itemStandard":"测试"}],"stepParam":"{\"rejectCondition\":{\"ruleContent\":\"当不满足条款数据大于等于1时，并且被评委否决人数大于等于1名时，否决投标人。\",\"unSatisfiedNum\":1,\"rejectNum\":1,\"investment\":null,\"creditScore\":null,\"bidderNum\":null,\"totalScore\":null,\"rank\":null},\"rejectType\":1}"},{"ifPqr":"false","ifSummarize":0,"ifReject":"true","ifBlindBid":"true","rejectType":1,"ifOpenComputeChange":"false","isExpand":"false","stepName":"技术审查","sort":2,"stepType":1,"items":[{"itemMinScore":11,"itemMaxScore":70,"itemName":"测试","itemStandard":"测试"}],"stepParam":"{\"weight\":100,\"standardScore\":70,\"ifSummarize\":0,\"rejectCondition\":{\"ruleContent\":\"汇总得分至少为30分，否则否决投标人。\",\"unSatisfiedNum\":1,\"rejectNum\":1,\"investment\":null,\"creditScore\":null,\"bidderNum\":null,\"totalScore\":30,\"rank\":null},\"rejectType\":1,\"ifReject\":1}","standardScore":70,"catalogId":""},{"ifPqr":"false","ifSummarize":"false","ifReject":"true","ifBlindBid":"false","rejectType":1,"ifOpenComputeChange":"false","isExpand":"false","stepName":"报价得分","sort":3,"stepType":2,"standardScore":30,"catalogId":"${catalogId}","stepParam":"{\"weight\":100,\"standardScore\":30,\"catalogId\":\"1887306232988766210\",\"ifOpenComputeChange\":0,\"standardPriceRule\":{\"computeMode\":2,\"computeFunType\":1,\"ruleContent\":\"系统将使用有效投标单位投标报价最低的报价为基准价。\"},\"quotationScoreRule\":{\"deductPointByHigh\":3,\"deductPointByLow\":3,\"deductPointTo\":0,\"computeFunType\":3,\"ruleContent\":\"以基准值为最高分Fmax，报价每高于基准报价1%时扣3分，报价每低于基准报价1%扣3分，最低扣至0分\"}}"}],"resultGatherModeParam":"{\"type\":1,\"recCandidateNum\":3,\"ruleContent\":\"以汇总得分由高到低依次推荐3名中标候选人。汇总得分相等时，投标报价低的优先；投标报价也相等的，技术得分高的优先；当技术得分也相等的，排名相同，最终汇总得分排名第一的确定为中标人。\"}","resultGatherModeDesc":"汇总得分 =  价格得分"}</t>
+    <t>{"scaleProcess":2,"ifOfferRank":"false","ifWeight":"false","ifCreditScore":"false","scorePrincipleType":0,"reviewer":"1","methodName":"0","ifCreditWeight":"false","ifSupportPreviewSumScore":"true","scorePrincipleParam":"{\"ruleContent\":\"汇总全部评分后，计算评分均值\"}","creditScoreParam":"{}","tfId":"${tfId}","steps":[{"ifPqr":"true","ifSummarize":"false","ifReject":"false","ifBlindBid":"false","rejectType":1,"ifOpenComputeChange":"false","isExpand":"false","stepName":"资格评审","sort":1,"stepType":0,"items":[{"itemName":"测试","itemStandard":"测试"}],"stepParam":"{\"rejectCondition\":{\"ruleContent\":\"当不满足条款数据大于等于1时，并且被评委否决人数大于等于1名时，否决投标人。\",\"unSatisfiedNum\":1,\"rejectNum\":1,\"investment\":null,\"creditScore\":null,\"bidderNum\":null,\"totalScore\":null,\"rank\":null},\"rejectType\":1}"},{"ifPqr":"false","ifSummarize":0,"ifReject":"true","ifBlindBid":"true","rejectType":1,"ifOpenComputeChange":"false","isExpand":"false","stepName":"技术审查","sort":2,"stepType":1,"items":[{"itemMinScore":11,"itemMaxScore":70,"itemName":"测试","itemStandard":"测试"}],"stepParam":"{\"weight\":100,\"standardScore\":70,\"ifSummarize\":0,\"rejectCondition\":{\"ruleContent\":\"汇总得分至少为30分，否则否决投标人。\",\"unSatisfiedNum\":1,\"rejectNum\":1,\"investment\":null,\"creditScore\":null,\"bidderNum\":null,\"totalScore\":30,\"rank\":null},\"rejectType\":1,\"ifReject\":1}","standardScore":70,"catalogId":""},{"ifPqr":"false","ifSummarize":"false","ifReject":"true","ifBlindBid":"false","rejectType":1,"ifOpenComputeChange":"false","isExpand":"false","stepName":"报价得分","sort":3,"stepType":2,"standardScore":30,"catalogId":"${catalogId}","stepParam":"{\"weight\":100,\"standardScore\":30,\"catalogId\":\"${catalogId}\",\"ifOpenComputeChange\":0,\"standardPriceRule\":{\"computeMode\":2,\"computeFunType\":1,\"ruleContent\":\"系统将使用有效投标单位投标报价最低的报价为基准价。\"},\"quotationScoreRule\":{\"deductPointByHigh\":3,\"deductPointByLow\":3,\"deductPointTo\":0,\"computeFunType\":3,\"ruleContent\":\"以基准值为最高分Fmax，报价每高于基准报价1%时扣3分，报价每低于基准报价1%扣3分，最低扣至0分\"}}"}],"resultGatherModeParam":"{\"type\":1,\"recCandidateNum\":3,\"ruleContent\":\"以汇总得分由高到低依次推荐3名中标候选人。汇总得分相等时，投标报价低的优先；投标报价也相等的，技术得分高的优先；当技术得分也相等的，排名相同，最终汇总得分排名第一的确定为中标人。\"}","resultGatherModeDesc":"汇总得分 =  价格得分"}</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -617,6 +617,7 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
